--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -2635,7 +2635,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137062771</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137063272</v>
       </c>
       <c r="B12" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137062790</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137062791</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>137062793</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137062794</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137063271</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>137062780</v>
       </c>
       <c r="B18" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137062771</v>
       </c>
       <c r="B11" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>137063272</v>
       </c>
       <c r="B12" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>137062790</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137062791</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>137062793</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>137062794</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137063271</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>137062780</v>
       </c>
       <c r="B18" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -1717,11 +1717,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långåker NV, Vb</t>
@@ -1834,11 +1830,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Täfteån, Vb</t>
@@ -1951,11 +1943,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långåker NV, Vb</t>
@@ -2068,11 +2056,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långåker NV, Vb</t>
@@ -2185,11 +2169,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långåker NV, Vb</t>
@@ -2304,11 +2284,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2422,11 +2398,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Täfteån, Vb</t>
@@ -2544,11 +2516,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Långåker NV, Vb</t>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137062771</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137063272</v>
       </c>
       <c r="B12" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>137062790</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>137062791</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>137062793</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137062794</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137063271</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137062780</v>
       </c>
       <c r="B18" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137062771</v>
       </c>
       <c r="B11" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137063272</v>
       </c>
       <c r="B12" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>137062790</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>137062791</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>137062793</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137062794</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137063271</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137062780</v>
       </c>
       <c r="B18" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137062771</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137063272</v>
       </c>
       <c r="B12" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>137062790</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>137062791</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>137062793</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137062794</v>
       </c>
       <c r="B16" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137063271</v>
       </c>
       <c r="B17" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137062780</v>
       </c>
       <c r="B18" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 38462-2026 artfynd.xlsx
+++ b/artfynd/A 38462-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137062767</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137062777</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137062789</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137062778</v>
       </c>
       <c r="B5" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137062776</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137062786</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137062772</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137062781</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137062782</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137062771</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
         <v>137063272</v>
       </c>
       <c r="B12" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>137062790</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>137062791</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>137062793</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>137062794</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
         <v>137063271</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>137062780</v>
       </c>
       <c r="B18" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137062784</v>
       </c>
       <c r="B19" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137062785</v>
       </c>
       <c r="B20" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
